--- a/artfynd/A 25098-2022 artfynd.xlsx
+++ b/artfynd/A 25098-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25098-2022 artfynd.xlsx
+++ b/artfynd/A 25098-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113870398</v>
+        <v>113870815</v>
       </c>
       <c r="B2" t="n">
-        <v>104650</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>F.d trädklädd betesmark Marma Alunda, Upl</t>
+          <t>Marma Alunda, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670415</v>
+        <v>670463</v>
       </c>
       <c r="R2" t="n">
-        <v>6663615</v>
+        <v>6663380</v>
       </c>
       <c r="S2" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -775,7 +777,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Aina Pihlgren</t>
+          <t>Aina Pihlgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,15 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113870396</v>
+        <v>113870398</v>
       </c>
       <c r="B3" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +799,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -895,6 +892,112 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113870396</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>F.d trädklädd betesmark Marma Alunda, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>670415</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6663615</v>
+      </c>
+      <c r="S4" t="n">
+        <v>44</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Aina Pihlgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25098-2022 artfynd.xlsx
+++ b/artfynd/A 25098-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113870815</t>
         </is>
       </c>
     </row>
@@ -891,6 +901,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113870398</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,8 +1012,18 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113870396</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>